--- a/mock_results/G513RM_PR1_Result_20260425.xlsx
+++ b/mock_results/G513RM_PR1_Result_20260425.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,11 +61,23 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +102,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
     <fill>
@@ -168,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,16 +209,28 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -568,13 +602,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E15"/>
+  <dimension ref="B1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
@@ -636,7 +670,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>AMD Ryzen 9 7945HX (Dragon Range)</t>
+          <t>AMD Ryzen 9 7945HX (Dragon Range, Zen4) + NVIDIA GeForce RTX 40 Series</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
@@ -650,7 +684,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Windows 11 23H2</t>
+          <t>Windows 11 23H2 (Build 22631)</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
@@ -708,7 +742,7 @@
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BD / SKU</t>
+          <t>BD / 料號</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -723,29 +757,51 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Panel</t>
+          <t>Panel / RAM</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>G513RM-HQ001</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Ryzen 9 7945HX</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>RTX 3060 6GB</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>15.6" FHD 165Hz</t>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>RTX 4070 8GB GDDR6</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>15.6" QHD 165Hz / 32GB DDR5-4800</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>G513RM-HQ002</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Ryzen 9 7945HX</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>RTX 4060 8GB GDDR6</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>15.6" QHD 165Hz / 32GB DDR5-4800</t>
         </is>
       </c>
     </row>
@@ -773,40 +829,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>▶  SKU：G513RM-HQ001</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>▶  SKU：G513RM-HQ001   |   G513RM-HQ002</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Test Item</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>G513RM-HQ001</t>
         </is>
       </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>G513RM-HQ002</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -814,12 +876,15 @@
           <t>MobileMark 25 — Modern Office (min)</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="10" t="n">
         <v>420</v>
       </c>
+      <c r="D3" s="10" t="n">
+        <v>445</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -827,34 +892,107 @@
           <t>MobileMark 25 — Video Playback (min)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="10" t="n">
         <v>562</v>
       </c>
+      <c r="D4" s="10" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>MobileMark 25 — Content Creation (min)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>385</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>PCMark 10 Battery — Modern Office (min)</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C6" s="10" t="n">
         <v>378</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="D6" s="10" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>PCMark 10 Battery — Video Playback (min)</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C7" s="10" t="n">
         <v>645</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Web Browsing (Edge / YouTube) (min)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>412</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Battery Capacity (Wh)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Charging Time: 0→100% (min)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -872,127 +1010,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>▶  SKU：G513RM-HQ001</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>▶  SKU：G513RM-HQ001   |   G513RM-HQ002</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Test Item</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>G513RM-HQ001</t>
         </is>
       </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>G513RM-HQ002</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 Multi (pts)</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
+          <t>Cinebench R23 — Multi-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>22450</v>
       </c>
+      <c r="D3" s="10" t="n">
+        <v>22380</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 Single (pts)</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
+          <t>Cinebench R23 — Single-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
         <v>1734</v>
       </c>
+      <c r="D4" s="10" t="n">
+        <v>1730</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R24 Multi (pts)</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
+          <t>Cinebench R24 — Multi-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>14980</v>
       </c>
+      <c r="D5" s="10" t="n">
+        <v>14920</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R24 Single (pts)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
+          <t>Cinebench R24 — Single-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>1178</v>
       </c>
+      <c r="D6" s="10" t="n">
+        <v>1174</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>PCMark 10 Overall (score)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
+          <t>Cinebench 2024 — Multi-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1388</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>PCMark 10 — Overall (score)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
         <v>7234</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>PCMark 10 Productivity (score)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
+      <c r="D8" s="10" t="n">
+        <v>7218</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>PCMark 10 — Productivity (score)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>8678</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>CrossMark Overall (score)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
+      <c r="D9" s="10" t="n">
+        <v>8654</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>PCMark 10 — Digital Content Creation (score)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>9340</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>9312</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>CrossMark — Overall (score)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>1812</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>CrossMark — Productivity (score)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>1908</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>3DMark CPU Profile — 1T (pts)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>1045</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>3DMark CPU Profile — Max Threads (pts)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>22380</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>22310</v>
       </c>
     </row>
   </sheetData>
@@ -1010,171 +1255,449 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>▶  SKU：G513RM-HQ001</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>▶  SKU：G513RM-HQ001   |   G513RM-HQ002</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Test Item</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>G513RM-HQ001</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>G513RM-HQ002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>GPU →</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>RTX 4070 8GB GDDR6</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>RTX 4060 8GB GDDR6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>▌ 3DMark Benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>3DMark Fire Strike (score)</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Fire Strike — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>20420</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>14560</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
+    <row r="6">
+      <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>3DMark Fire Strike Extreme (score)</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Fire Strike — Physics Score</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>21580</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>21420</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Fire Strike Extreme — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>10580</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>7420</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Fire Strike Ultra — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>5890</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Time Spy — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>13240</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>9340</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Time Spy — CPU Score</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>10820</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>10780</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Time Spy Extreme — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>6590</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>4680</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Port Royal — Score</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>9480</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>6620</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Speed Way — Score</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>3820</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>▌ Gaming FPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077 — 1080p Ultra RT (fps)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077 — 1080p Ultra RT + DLSS Quality (fps)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>3DMark Time Spy (score)</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>9340</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077 — 1440p Ultra RT (fps)</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>3DMark Time Spy Extreme (score)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>4680</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077 — 1440p Ultra RT + DLSS Quality (fps)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Cyberpunk 2077 1080p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Alan Wake 2 — 1080p Ultra RT (fps)</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Cyberpunk 2077 1440p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Alan Wake 2 — 1080p Ultra RT + DLSS Quality (fps)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Red Dead Redemption 2 1080p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>F1 2024 — 1080p Ultra (fps)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>138</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Red Dead Redemption 2 1440p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>F1 2024 — 1440p Ultra (fps)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>CS2 — 1080p High (fps)</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>298</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>DOTA 2 — 1080p Ultra (fps)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>198</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Red Dead Redemption 2 — 1080p Ultra (fps)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Elden Ring — 1080p Max Settings (fps)</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>108</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Black Myth: Wukong — 1080p Epic (fps)</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
         <v>38</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>F1 2024 1080p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>F1 2024 1440p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>74</v>
+      <c r="D27" s="10" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Black Myth: Wukong — 1080p Epic + DLSS Quality (fps)</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1187,22 +1710,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>HW Info — 系統規格摘要</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Project Code</t>
         </is>
@@ -1214,158 +1737,206 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>SKU / BD</t>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Phase</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>PR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>BD / 料號</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>G513RM-HQ001</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Ryzen 9 7945HX</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>GPU</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>RTX 3060 6GB</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>RTX 4070 8GB GDDR6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Panel</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>15.6" FHD 165Hz</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>15.6" QHD 165Hz IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>RAM</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>32GB DDR5-4800</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>32GB DDR5-4800 (SO-DIMM×2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>1TB PCIe 4.0 NVMe</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>1TB Samsung 990 Pro PCIe 4.0 NVMe</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>90Wh</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>OS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Windows 11 23H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Windows 11 23H2 (Build 22631)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>BIOS Ver.</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>G513RM.318</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>EC Ver.</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>G513RM.115</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Driver — GPU</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>572.60</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Driver — LAN</t>
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>GPU Driver</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>572.60 (WHQL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>LAN Driver</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>12.19.2.60</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Driver — Audio</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Audio Driver</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>6.0.9550.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Turbo Mode TDP (W)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>50 / 45 (SKU HQ002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Standard TDP (W)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Fan Mode tested</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Turbo Mode (Manual)</t>
         </is>
       </c>
     </row>
